--- a/data/raw/darkbirth_customerList.xlsx
+++ b/data/raw/darkbirth_customerList.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2134,6 +2134,77 @@
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>오부장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>경찰청교육관</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>010-2653-4166</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>부평구</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0-10</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>45-80</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0-10000</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0-400</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>경찰청교육관_01026534166</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>{"region":"부평구","floor":"0-10","area_real":"45-80","deposit":"0-10000","rent":"0-400","premium":"0"}</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>darkbirth@naver.com</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2025-09-09T03:33:47.903Z</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
